--- a/backend/excel/Candidates.xlsx
+++ b/backend/excel/Candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,44 +563,72 @@
           <t>Software &amp; IT</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Software &amp; IT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Python, FastAPI, SQLite</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>SQLite</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>FastAPI</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Bachelor of Science from MIT</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Python, FastAPI, SQLite</t>
+          <t>Senior Software Engineer, Software Engineer, Python, FastAPI, SQLite, Computer Science, MIT, Bachelor of Science, Databases, Software Development</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Extracted using rule-based fallback.</t>
+          <t>John Doe is a Senior Software Engineer with a Bachelor of Science in Computer Science from MIT. He has experience developing FastAPI services and databases using Python and SQLite.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/0e520716873d483bbd4a995a2092a714_normal.pdf</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/b32dcc45ea4041adb732cf3e194fb092_normal.pdf</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2026-08-07 11:35:42</t>
+          <t>2026-08-09 11:24:00</t>
         </is>
       </c>
     </row>
@@ -610,7 +638,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -629,44 +657,64 @@
           <t>Software &amp; IT</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Docker, C++</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>C++ Software Developer</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Docker, C++</t>
+          <t>Bob Johnson, C++, Docker, Microsoft, C++ Software Developer, Software Developer, Developer, Software, C++ Expert, Docker Intermediate</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Extracted using rule-based fallback.</t>
+          <t>Bob Johnson is a C++ Software Developer with experience working at Microsoft. He possesses expert-level skill in C++ and intermediate-level skill in Docker.</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/7cc1d2c078de41ce82a4248386ba752f_normal.docx</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/a50a3adaa43a4fd19002d89116dd90e0_normal.docx</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-08-07 11:35:55</t>
+          <t>2026-08-09 11:24:26</t>
         </is>
       </c>
     </row>
@@ -695,44 +743,60 @@
           <t>Software &amp; IT</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Deep Learning</t>
+          <t>Deep Learning</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>MS from Stanford University</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>ML Research Engineer</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Deep Learning</t>
+          <t>ML Research Engineer, TensorFlow, PyTorch, Deep Learning, Stanford University, MS in AI, Artificial Intelligence, Machine Learning, ML, Research Engineer, AI</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Extracted using rule-based fallback.</t>
+          <t>ML Research Engineer with experience utilizing TensorFlow, PyTorch, and Deep Learning. Holds an MS in AI from Stanford University.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/2399386699394d6a831428ff581a1442_scanned.pdf</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/462cdb83db094eadbf9587b17b3b5bf2_scanned.pdf</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2026-08-07 11:35:25</t>
+          <t>2026-08-09 11:23:46</t>
         </is>
       </c>
     </row>
@@ -742,32 +806,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RAJESH KUMAR YADAV</t>
+          <t>Uma Sankar Panda</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rajeshkyadav00342@gmail.com</t>
+          <t>umasankarpanda012@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+91 8107261166</t>
+          <t>+91 7978021431</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhiwadi, Rajasthan, India</t>
+          <t>Ganjam, Odisha, India</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Transportation &amp; Logistics</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas / Manufacturing</t>
+          <t>Logistics &amp; Supply Chain</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -776,73 +840,65 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Piping Inspection, QA/QC Inspection, Quality KPIs, Final Inspection, Vendor Inspection, IQC, NDT Level II, UT, MT, PT, VT, Material UTM Tested, Root Cause Analysis, Dimensional Inspection, Documentation Control, Audit Readiness, Inspection Planning, Defect Reduction, Compliance, Network Optimization, Diagnostics, Preventive Maintenance</t>
+          <t>Logistics Coordinator, Time Keeper, Stock Management, Team Management, Market Development, Strategic Planning, Relationship Building, Recruitment, Logistics Management</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Process Improvement, Problem Solving, Cross-functional Coordination, Troubleshooting, Corrective Action, Preventive Action, Technical Support</t>
+          <t>Hard Working, Communication</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Micrometers, Bevel Protractor, Wire Gauge, Rockwell Hardness Tester, Profile Projector, Internal Taper &amp; External Tapper Gauge, Portable Hardness Tester, Bore Dial Gauge, Universal Testing Machine, Contour, Vernier Caliper ( Manual &amp; Digital ), Surface Roughness Testers</t>
+          <t>Basic Computer Science</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Micrometers, Bevel Protractor, Wire Gauge, Rockwell Hardness Tester, Profile Projector, Internal Taper &amp; External Tapper Gauge, Portable Hardness Tester, Bore Dial Gauge, Universal Testing Machine, Contour, Vernier Caliper, Surface Roughness Testers</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ASME Section V, ISO 9001, API, SOPs</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>APQP, PPAP, SPC, FMEA, MSA, PDCA, CAPA, NCR, 8D, ITP, FIFO, QMS</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>English, Hindi, Oriya</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Bachelor of Technology (B.Tech) from SLBS Engineering College | Senior Secondary Education from CBSE Board</t>
+          <t>Master Of Business Administration from Apex Professional University, Arunachal Pradesh | P.G.D.C.A from Berhampur, Odisha | Bachelor Of Arts from Berhampur Univercity, Ganjam, Odisha | Higher Secondary from CHSE Odisha</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>WELLCARE Oil Tools Pvt. Ltd</t>
+          <t>Sri Ram Enterprises</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Quality Engineer / Inspection Engineer</t>
+          <t>Logistics Coordinator &amp; Time Keeper</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Mechanical Quality Engineer, Quality Engineer, Inspection Engineer, QA/QC Inspection, APQP, PPAP, SPC, FMEA, MSA, ASME Section V, ISO 9001, API, NDT Level II, 8D, CAPA, QMS, Piping Inspection, Root Cause Analysis, Micrometers, Vernier Caliper, UT, MT, PT, VT</t>
+          <t>Logistics Coordinator, Time Keeper, Stock Management, Team Management, Market Development, Marketing Manager, Territory Sales Manager, Logistics Manager, Recruitment, Strategic Planning, Relationship Building, MBA, P.G.D.C.A, Logistics Department</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Process Quality Assurance professional with over 6 years of experience in quality assurance and quality control, specializing in process improvement, defect analysis, and QMS compliance. Adept in utilizing precision measurement tools and executing ASNT NDT Level II inspections (UT, MT, PT, VT) in accordance with ASME Section V, API, and ISO 9001 standards. Proven track record of boosting production output by 40% and reducing defect rates to under 2% through root cause analysis using 8D and CAPA methodologies.</t>
+          <t>Hard Working and Driven Sales Management and Logistics Professional equipped to revitalize logistics operations and sales alignment procedures. Experienced with leading sales teams, managing key accounts, and coordinating logistics departments to maximize profits, client acquisition, and operational accuracy.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/b65f10e568e74c53a8c1624afc33d58b_REAJESHRESUMEAEW.pdf</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/6959d7eeff6242fc963cc16064fcb11d_Uma Sankar  (1).pdf</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-08-07 13:27:09</t>
+          <t>2026-08-09 12:27:04</t>
         </is>
       </c>
     </row>
@@ -852,95 +908,107 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MANAVVAR</t>
+          <t>RAJESH KUMAR YADAV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>manavvarch827@gmail.com</t>
+          <t>rajeshkyadav00342@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+91 875511234</t>
+          <t>+91 8107261166</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Muzaffarnagar, UP, (NCR)</t>
+          <t>Bhiwadi, Rajasthan, India</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Transportation &amp; Logistics</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Retail &amp; Sales</t>
+          <t>Oil &amp; Gas</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Inventory Management, Logistics Coordination, Team Supervision, Workflow Optimization</t>
+          <t>Piping Inspection, QA/QC Inspection, Final Inspection, Vendor Inspection, IQC, NDT Level II, Material UTM Tested, Dimensional inspections, VT, MT, PT, UT, Broadband, leased line, MPLS, VPN, enterprise connectivity, network infrastructure, Commissioning, installation, testing, startup, welding, fabrication alignments</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Creativity, Negotiation, Critical Thinking, Leadership, Communication</t>
+          <t>collaborated &amp; communicated with Team, Problem Solving, Cross-functional Coordination, Troubleshooting, Corrective Action, Preventive Action, Defect Reduction, Compliance, operator training</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>E-Way Bill Portal, Babylon App, MS Excel</t>
+          <t>Micrometers, Bevel Protractor, Wire Gauge, Rockwell Hardness Tester, Profile Projector, Internal Taper &amp; External Tapper Gauge, Portable Hardness Tester, Bore Dial Gauge, Universal Testing Machine, Contour, Vernier Caliper, Surface Roughness Testers</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Universal Testing Machine, MDF plant</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ASME Section V, ISO 9001, API, ASME, SOPs</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>APQP, PPAP, SPC, FMEA, MSA, PDCA, CAPA, NCR, 8D, FIFO, QMS, ITPs, Quality Plans, Quality KPIs, Documentation Control, Audit Readiness, Inspection Planning, Preventive maintenance planning</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Bachelor of Business Administration from MAHARAJA AGRASEN HIMALAYAN GARHWAL UNIVERSITY, UTTARAKHAND | INTERMEDIATE from The Skyland School | HIGH SCHOOL from The Skyland School</t>
+          <t>Bachelor of Technology (B.Tech) from SLBS Engineering College | Senior Secondary Education from CBSE Board</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>MYNTRA</t>
+          <t>WELLCARE Oil Tools Pvt. Ltd</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Team Leader</t>
+          <t>Quality Engineer / Inspection Engineer</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Team Leader, Logistics Coordination, E-Way Bill, E-Way Bill Portal, Babylon App, Inventory Management, Team Supervision, MS Excel, Workflow Optimization, Myntra, BBA, Business Administration</t>
+          <t>Mechanical Quality Engineer, Quality Engineer, Inspection Engineer, Process Quality Assurance Engineer, APQP, PPAP, Root Cause Analysis, QA/QC, NDT Level II, 8D, ASME Section V, ISO 9001, API, QMS, UT, MT, PT, VT, Piping Inspection, SPC, FMEA, MSA, IQC</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Motivated and detail-oriented professional with a Bachelor of Business Administration and hands-on experience as a Team Leader in logistics and item tracking systems at MYNTRA. Experienced in Logistics Coordination, E-Way Bill generation, and digital tracking systems like the Babylon App, with a proven ability to lead cross-functional teams and improve workflow efficiency.</t>
+          <t>Process Quality Assurance professional with over 6 years of experience in quality assurance and quality control, specializing in process improvement and defect analysis. Proven track record of amplifying production output by 40% and reducing error rates to below 2%. Seeking a Process Quality Assurance Engineer position to apply expertise in APQP, PPAP, Root Cause Analysis (8D), QMS (API, ISO 9001, ASME), and NDT Level II inspections (UT, MT, PT, VT).</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/9eac0c77f5784a71829edeb8dbe7bd87_Manavvar_Resume.pdf</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/84f3c3c5e261468db59066f06e92a16a_REAJESHRESUMEAEW.pdf</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2026-08-07 13:28:36</t>
+          <t>2026-08-09 17:46:05</t>
         </is>
       </c>
     </row>
@@ -950,62 +1018,66 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ANUJ KUMAR SHARMA</t>
+          <t>RITESH KUMAR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anujsharma3j@gmail.com</t>
+          <t>roshankumar965149@gmail.co</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7318559332</t>
+          <t>7887227480</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ghazipur, U.P., India</t>
+          <t>GORAKHPUR, UTTAR PRADESH, India</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Skilled Trades</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Automotive Manufacturing</t>
+          <t>Power Transmission</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Entry</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Seat Assembly, Production, Quality Control, Motion Study, Method Study</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>HV Transmission Line Construction, HV Transmission Line Maintenance, tower foundation, tower erection, stringing, sagging, conductor installation, route surveys, fault identification, fault resolution</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Active Listening, Hardworking, Keen Observer, Better Scheduling, Problem-solving, Flexibility, Dedication, Continuous learning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Vernier Calliper, Micrometer, Height Gauge, Microsoft Office, SAP</t>
+          <t>transmission line tools</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Vernier Calliper, Micrometer, Height Gauge</t>
+          <t>winches, pullers, tensioners, lifting equipment</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>5S, 7QC TOOL, PDCA, CAPA</t>
+          <t>safety regulations, work permits, PPE requirements, quality standards</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1013,44 +1085,40 @@
           <t>Hindi, English</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>PDCA, CAPA, 3M, Why Why analysis, Kaizen, Poka Yoke, Red bin analysis, 8 wastes of Lean, M change, Cycle time, Lead time, Talk time, Through put time, Motion Study, Method Study, LEAN Manufacturing</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>B.tech from RGPV (Bhopal) | Diploma from Patel Groups of Institute ( Bhopal) | 10th from BSEB</t>
+          <t>School Secretary education from Gandhi Inter College Mahuapar | Intermediate from National Inter college Barhalganj Gorakhpur | ITI from BARHALGANJ PRIVATE ITI | Bachelor of Science from H.M.MAHAVIDYAL PIWATAL MAU</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Krishna Maruti Limited</t>
+          <t>Rohini Industrial Electricals Pvt. Ltd.</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Operator Engineer Training</t>
+          <t>TRANSMISSION LINE TECHNICIAN</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Mechanical Engineering, Operator Engineer Training, Technical assistant, Production, POKA-YOKE, 5S, Kaizen, PDCA, CAPA, 7QC TOOL, LEAN Manufacturing, Vernier Calliper, Micrometer, Height Gauge, SAP, Suzuki Motor Gujarat, Krishna Maruti Limited, Minda Corporation, Assembly Shop</t>
+          <t>Transmission Line Technician, HV Transmission Line, Tower Erection, Stringing, Sagging, Conductor Installation, Tower Foundation, Winches, Pullers, Tensioners, Electrician, ITI Electrician, High Voltage, Route Surveys, Lifting Equipment, Electrical Contractors</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Mechanical Engineering professional with experience as an Operator Engineer Trainee at Krishna Maruti Limited and a Technical Assistant in Production at Minda Corporation. Experienced in maintaining production quality standards, implementing Poka-Yoke, 5S, and manufacturing methodologies such as Kaizen, CAPA, PDCA, and lean tools.</t>
+          <t>Dedicated Transmission Line Technician with over 5 years of experience in HV Transmission Line Construction and Maintenance projects. Skilled in tower foundation, tower erection, stringing, sagging, and conductor installation activities. Proficient in handling specialized tools, winches, pullers, tensioners, and lifting equipment while maintaining high safety and quality standards.</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/37b6ef0abf6048deb245e47830017c0c_ANUJ RESUME-1.pdf</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/b7231dd1c41c4cbbbb1f8cfc748f5ff3_RITESH KUMAR TRANSMISSION LINE TECHNICIAN.pdf</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-08-08 18:58:25</t>
+          <t>2026-08-09 12:28:23</t>
         </is>
       </c>
     </row>
@@ -1060,315 +1128,103 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NAQVI AGAZ HAIDER</t>
+          <t>Sunil Kumar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>agaz3110@gmail.com</t>
+          <t>sk8913471@rmaii.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+91 9619088263</t>
+          <t>10419400744</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Siwan, Bihar, India</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Transportation &amp; Logistics</t>
+          <t>Skilled Trades</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Travel &amp; Tourism</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Senior</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>PNR Creation, Complex Routing, Fare Construction, Ticketing Operations, Involuntary Exchange, MCO, LCC, IRROPs Handling, Issue, Reissue, Revalidation</t>
+          <t>Electrical installations, Electrical maintenance, Fire alarm systems installation, Fire alarm systems troubleshooting, Building Management Systems (BMS) operations, Industrial Wiring, B.M.S Working, Fire alarm Working</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Customer Service, Upselling, Problem-Solving, Communication</t>
+          <t>honest</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Amadeus, Sabre, Focal Scope, Microsoft Office</t>
+          <t>SIGA-PD, SIGA-SB, SIGA-LED, SIGA-CT1, SIGA-CT2, SIGA-IM, SIGA-CC1, BeamDetector EC-100R, MPSR2-SHTW-GE</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>SLA, TAT</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>smoke detector, heat detector, beam detector, WP Enclosure modules</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hindi, English</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Bachelor of Science from VES College of Arts, Science and Commerce | HSC from Shree Sanatan Dharam Vidyalaya</t>
+          <t>10th Passed from Bihar Board</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>ATPI – GTS E-Services Pvt. Ltd.</t>
+          <t>Bahwan Engineering Company</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Marine Travel Consultant</t>
+          <t>Industrial Wiring Electrician</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Marine Travel Consultant, Corporate Travel Consultant, Travel Consultant, Amadeus, Sabre, GDS, PNR Creation, Complex Routing, Fare Construction, Ticketing Operations, Focal Scope, SLA, TAT</t>
+          <t>Industrial Wiring Electrician, Electrician, Wireman, Electrical installations, Electrical maintenance, Fire alarm systems, BMS, Building Management Systems, Airport Project, Oman, Qatar, Haryana, Bihar Board, SIGA-PD, BeamDetector</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Travel consultant with 4+ years of progressive experience spanning retail, corporate, and marine travel. Advanced from a client-facing associate role into specialized marine and corporate travel consulting. Expert in Amadeus and Sabre GDS platforms, complex fare construction, and multi-modal itinerary management, with a track record of improving client satisfaction and reducing ticketing discrepancies through process discipline and strong SLA/TAT compliance.</t>
+          <t>Experienced Industrial Wiring Electrician with over 11 years of hands-on experience in electrical installations, maintenance, fire alarm systems troubleshooting, and Building Management Systems (BMS). Proven background working on key international infrastructure projects including the MC-12 Airport in Muscat, Oman, alongside industrial roles in Qatar and India.</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/2e43fb64bfe141249035fb381c7de30c_Agaz_Haider_Resume.pdf</t>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/4d1d0b372c7a4ba2b166cf8c86c8f2ab_SUNIL KUMAR PDF_merged.pdf</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-08-08 19:02:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mohd Asif</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>mohdasif11sep3@gmail.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+91 97925 29770</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Uttar Pradesh, 272173</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Entry</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Data Entry, Typing, Social Media Analytics, SEO, Online Growth Strategies, Record maintenance</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Strategic Teamwork, Customer Support, Product positioning, Stakeholder relationship management, Professional efficiency</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Microsoft Excel</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>English, Hindi, Urdu</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Direct-to-consumer awareness, Field marketing</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>MBA from Dr. Rizvi College of Engineering (AKTU Lucknow) | Bachelor of Science from Siddharth University, Kapilvastu</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Indian Oil Corporation Limited</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Admin &amp; Account Assistant</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>MBA Graduate, Marketing Specialist, Data Entry, Microsoft Excel, Medicine Marketing, Office Operations, Pharma Sales, Customer Support, Typing, Google Digital Marketing, Social Media Analytics, SEO, Online Growth Strategies, Field Marketing, Direct-to-consumer awareness, Product positioning, Stakeholder relationship management</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>An MBA graduate and Marketing Specialist with a background in science. Combines analytical precision with practical experience in pharmaceutical field marketing and administrative office operations, including data entry and customer support.</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/ee8c2dd415a94120a21a2657f04db040_ASIF NEW CV MBA - 2026.pdf</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2026-08-08 19:02:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SHAIKH ANAS Z.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sanas8084@gmail.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>+91 7817937498</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ahmedabad, India</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Software &amp; IT</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Laptop assembling, Laptop disassembling, Computer assembling, Computer disassembling, Troubleshooting hardware issues, Develop and test computer systems, Develop and test computer components, Windows installation, Windows management, Crimping, punching, Basic networking setup, Network troubleshooting, Formatting Windows, Device driver installation, Software installation</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teamwork, communication, Ability to work independently, Adaptable, willingness to learn, Positive attitude</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>MS Office Suite, Windows 7, Windows 8, Windows 10, Windows Server 2013, Windows Server 2016, Windows Server 2019</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Laptop, Computer, Servers</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>English, Hindi, Gujarati</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>System Administration, Help Desk, Technical Support</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Bachelor of Commerce (B.Com) from Vivekanand Vanijya College, Raipur, Ahmedabad. Gujarat University | Higher Secondary (12th) from GSEB | Secondary (10th) from GSEB</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Arizona Automation &amp; Technology</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Desktop Support Server Engineer</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>IT Hardware Engineer, Desktop Support Server Engineer, Technical Support Engineer, Desktop Support Engineer, Hardware Technician, Windows Server 2019, Windows Server 2016, Windows Server 2013, System Administration, Hardware Troubleshooting, Network Troubleshooting, OS installation, MS Office Suite, Help Desk Support, Assembling, Crimping &amp; punching</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Dedicated IT Hardware Engineer with over 7 years of experience in computer hardware, operating systems installation, and technical support. Proven expertise in troubleshooting hardware and network issues, laptop and computer assembly/disassembly, server administration, and desktop support.</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/50e26c351e5b463fa0957f9e1ade0da0_Cv - Shaikh Anas.pdf</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2026-08-08 19:02:44</t>
+          <t>2026-08-09 17:29:08</t>
         </is>
       </c>
     </row>

--- a/backend/excel/Candidates.xlsx
+++ b/backend/excel/Candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,6 +1228,120 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jaydeep Babubhai Ajani</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jaydeepajani1963@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+91 83470 50997</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rajkot, Gujarat, India</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Manufacturing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CNC Automation</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Junior</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>PLC programming, CNC machine commissioning, HMI development, troubleshooting, FAT/SAT testing, root-cause analysis, I/O mapping, parameter configuration, signal validation, synchronized axis control, coordinated machining operations</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Analytical &amp; problem solving, Self-motivated, Process-orientated</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Fanuc NC Guide, Fanuc Servo Guide, Fanuc Picture, GX Works, Fanuc Ladder, Microsoft Office Suite</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>CNC machines, Huron Graffenstaden CNC machines, Fanuc controllers, Mitsubishi controllers, spindle drives, servo axes, ATC systems, rotary/tilting tables, bar feeders, gantry robots, hydraulic units, pneumatic units, Arduino, IOT controller</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>CE safety standards, European machine directives, 5S</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gujarati, English, Hindi</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>PLC ladder logic</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Bachelor of Engineering from Marwadi Engineering College</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Ltd.</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Junior Engineer, R&amp;D Department</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Electrical Engineer, CNC Automation, PLC programming, Fanuc, Mitsubishi PLC, CNC machine commissioning, HMI development, Huron Graffenstaden, CE safety standards, Fanuc Ladder, GX Works, Fanuc NC Guide, Fanuc Servo Guide, Fanuc Picture, Bosch Rexroth PLC, Arduino, FAT/SAT testing, Troubleshooting, Servo axes</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Electrical Engineer with experience in CNC automation and PLC programming, seeking a challenging role in the automation industry. Possesses a strong background in Fanuc &amp; Mitsubishi PLC systems, CNC machine commissioning, HMI development, and troubleshooting.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>/Users/kunalsrivastav/Desktop/resume_parser/backend/uploads/6f5313762ca44452a4578057d4ffabec_JAYDEEP CV.pdf</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-08-09 21:40:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backend/excel/Candidates.xlsx
+++ b/backend/excel/Candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1342,6 +1342,100 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kunal Srivastav</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>kunal@example.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+91-9876543210</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Software &amp; IT</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Software &amp; IT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Python, FastAPI, React, PyTorch, FAISS, Docker</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>FastAPI, React, PyTorch</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>B.Tech from None</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Tech Corp</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Software Engineer, Tech Corp, Python, FastAPI, React, PyTorch, FAISS, Docker, B.Tech, Computer Science, Kunal Srivastav</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Software Engineer with experience at Tech Corp since 2022. Skilled in Python, FastAPI, React, PyTorch, FAISS, and Docker. Holds a B.Tech in Computer Science.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>mock_resume_9.pdf</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-08-11 15:14:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
